--- a/artfynd/A 73845-2021 artfynd.xlsx
+++ b/artfynd/A 73845-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 73845-2021 artfynd.xlsx
+++ b/artfynd/A 73845-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>60950457</v>
+        <v>60950448</v>
       </c>
       <c r="B12" t="n">
-        <v>89392</v>
+        <v>78503</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580487.0845707168</v>
+        <v>580462.9433546464</v>
       </c>
       <c r="R12" t="n">
-        <v>7036533.982239353</v>
+        <v>7036727.181255613</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>60950448</v>
+        <v>110963003</v>
       </c>
       <c r="B13" t="n">
-        <v>78503</v>
+        <v>78578</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,38 +1919,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grundtjärnsflon, Ång</t>
+          <t>Långtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580462.9433546464</v>
+        <v>580533.4980759874</v>
       </c>
       <c r="R13" t="n">
-        <v>7036727.181255613</v>
+        <v>7036488.601026244</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1977,22 +1978,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2016-08-09</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2016-08-09</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,22 +2013,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristin Lindström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristin Lindström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110963003</v>
+        <v>110963068</v>
       </c>
       <c r="B14" t="n">
-        <v>78578</v>
+        <v>89686</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2041,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2060,10 +2066,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580533.4980759874</v>
+        <v>580500.0067086458</v>
       </c>
       <c r="R14" t="n">
-        <v>7036488.601026244</v>
+        <v>7036536.993588337</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2106,11 +2112,6 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110963068</v>
+        <v>110964322</v>
       </c>
       <c r="B15" t="n">
-        <v>89686</v>
+        <v>56543</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2153,35 +2154,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580500.0067086458</v>
+        <v>580474.9906232045</v>
       </c>
       <c r="R15" t="n">
-        <v>7036536.993588337</v>
+        <v>7036533.677446748</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2213,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2223,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2250,7 +2256,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110964322</v>
+        <v>110964083</v>
       </c>
       <c r="B16" t="n">
         <v>56543</v>
@@ -2292,14 +2298,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långtjärnsberget, Ång</t>
+          <t>Långtjärnsberget (Långtjärnsberget), Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580474.9906232045</v>
+        <v>580467.9580286704</v>
       </c>
       <c r="R16" t="n">
-        <v>7036533.677446748</v>
+        <v>7036670.464635232</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2368,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110964083</v>
+        <v>110963339</v>
       </c>
       <c r="B17" t="n">
-        <v>56543</v>
+        <v>89405</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,40 +2390,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långtjärnsberget (Långtjärnsberget), Ång</t>
+          <t>Långtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580467.9580286704</v>
+        <v>580369.4316446291</v>
       </c>
       <c r="R17" t="n">
-        <v>7036670.464635232</v>
+        <v>7036489.391532029</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2449,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2459,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110963339</v>
+        <v>110963383</v>
       </c>
       <c r="B18" t="n">
-        <v>89405</v>
+        <v>89686</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2502,21 +2503,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2599,10 +2600,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110963383</v>
+        <v>110963478</v>
       </c>
       <c r="B19" t="n">
-        <v>89686</v>
+        <v>89405</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,21 +2616,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2640,10 +2641,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580369.4316446291</v>
+        <v>580392.2060032815</v>
       </c>
       <c r="R19" t="n">
-        <v>7036489.391532029</v>
+        <v>7036510.554814223</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2675,7 +2676,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2685,7 +2686,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2712,10 +2713,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110963478</v>
+        <v>110963527</v>
       </c>
       <c r="B20" t="n">
-        <v>89405</v>
+        <v>89686</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2728,21 +2729,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2753,10 +2754,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580392.2060032815</v>
+        <v>580377.8361235717</v>
       </c>
       <c r="R20" t="n">
-        <v>7036510.554814223</v>
+        <v>7036529.440192995</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2825,10 +2826,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110963527</v>
+        <v>110964052</v>
       </c>
       <c r="B21" t="n">
-        <v>89686</v>
+        <v>89423</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2841,35 +2842,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långtjärnsberget, Ång</t>
+          <t>Långtjärnsberget (Långtjärnsberget), Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580377.8361235717</v>
+        <v>580467.9580286704</v>
       </c>
       <c r="R21" t="n">
-        <v>7036529.440192995</v>
+        <v>7036670.464635232</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2938,10 +2939,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>110964052</v>
+        <v>110963186</v>
       </c>
       <c r="B22" t="n">
-        <v>89423</v>
+        <v>89405</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2954,35 +2955,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långtjärnsberget (Långtjärnsberget), Ång</t>
+          <t>Långtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580467.9580286704</v>
+        <v>580487.8143536373</v>
       </c>
       <c r="R22" t="n">
-        <v>7036670.464635232</v>
+        <v>7036522.810469956</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3014,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3024,7 +3025,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,10 +3052,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110963186</v>
+        <v>110963918</v>
       </c>
       <c r="B23" t="n">
-        <v>89405</v>
+        <v>56398</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3067,35 +3068,53 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580487.8143536373</v>
+        <v>580475.6009630479</v>
       </c>
       <c r="R23" t="n">
-        <v>7036522.810469956</v>
+        <v>7036633.954932846</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3127,7 +3146,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3137,7 +3156,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3164,10 +3183,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110963918</v>
+        <v>110964305</v>
       </c>
       <c r="B24" t="n">
-        <v>56398</v>
+        <v>89405</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3180,53 +3199,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580475.6009630479</v>
+        <v>580474.9906232045</v>
       </c>
       <c r="R24" t="n">
-        <v>7036633.954932846</v>
+        <v>7036533.677446748</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3295,10 +3296,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>110964305</v>
+        <v>110963759</v>
       </c>
       <c r="B25" t="n">
-        <v>89405</v>
+        <v>89686</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3311,21 +3312,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3336,10 +3337,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580474.9906232045</v>
+        <v>580371.381855763</v>
       </c>
       <c r="R25" t="n">
-        <v>7036533.677446748</v>
+        <v>7036643.415111532</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3408,10 +3409,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>110963759</v>
+        <v>110963012</v>
       </c>
       <c r="B26" t="n">
-        <v>89686</v>
+        <v>78512</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3420,25 +3421,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3449,10 +3450,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580371.381855763</v>
+        <v>580533.4980759874</v>
       </c>
       <c r="R26" t="n">
-        <v>7036643.415111532</v>
+        <v>7036488.601026244</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3484,7 +3485,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3494,7 +3495,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3521,10 +3522,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>110963012</v>
+        <v>111011502</v>
       </c>
       <c r="B27" t="n">
-        <v>78512</v>
+        <v>77515</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3533,39 +3534,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580533.4980759874</v>
+        <v>580543.0784167992</v>
       </c>
       <c r="R27" t="n">
-        <v>7036488.601026244</v>
+        <v>7036517.489708784</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3597,7 +3600,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3607,7 +3610,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3616,6 +3619,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3638,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111011502</v>
+        <v>111011446</v>
       </c>
       <c r="B28" t="n">
-        <v>77515</v>
+        <v>78578</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3650,21 +3654,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3677,10 +3681,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580543.0784167992</v>
+        <v>580566.255803163</v>
       </c>
       <c r="R28" t="n">
-        <v>7036517.489708784</v>
+        <v>7036646.983038193</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3750,10 +3754,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111011446</v>
+        <v>111011467</v>
       </c>
       <c r="B29" t="n">
-        <v>78578</v>
+        <v>89369</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3762,25 +3766,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3793,10 +3797,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580566.255803163</v>
+        <v>580506.0056203741</v>
       </c>
       <c r="R29" t="n">
-        <v>7036646.983038193</v>
+        <v>7036619.055564463</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3863,122 +3867,6 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>111011467</v>
-      </c>
-      <c r="B30" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Långtjärnsberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>580506.0056203741</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7036619.055564463</v>
-      </c>
-      <c r="S30" t="n">
-        <v>25</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Edsele</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2023-07-21</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2023-07-21</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
